--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -13262,10 +13262,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117955243</v>
+        <v>117955219</v>
       </c>
       <c r="B102" t="n">
-        <v>104929</v>
+        <v>96791</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13278,43 +13278,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ulva (Ulva), Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>620345</v>
+        <v>620352</v>
       </c>
       <c r="R102" t="n">
-        <v>6568134</v>
+        <v>6568133</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13346,7 +13337,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>01:01</t>
+          <t>00:55</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13356,7 +13347,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>01:01</t>
+          <t>00:55</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13388,10 +13379,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117955219</v>
+        <v>117955243</v>
       </c>
       <c r="B103" t="n">
-        <v>96791</v>
+        <v>104929</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13404,34 +13395,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ulva (Ulva), Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>620352</v>
+        <v>620345</v>
       </c>
       <c r="R103" t="n">
-        <v>6568133</v>
+        <v>6568134</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>01:01</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>01:01</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -13134,7 +13134,7 @@
         <v>117843415</v>
       </c>
       <c r="B101" t="n">
-        <v>104929</v>
+        <v>104931</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13262,10 +13262,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117955219</v>
+        <v>117955243</v>
       </c>
       <c r="B102" t="n">
-        <v>96791</v>
+        <v>104931</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13278,34 +13278,43 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ulva (Ulva), Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>620352</v>
+        <v>620345</v>
       </c>
       <c r="R102" t="n">
-        <v>6568133</v>
+        <v>6568134</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13337,7 +13346,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>01:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13347,7 +13356,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>01:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13379,10 +13388,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117955243</v>
+        <v>117955219</v>
       </c>
       <c r="B103" t="n">
-        <v>104929</v>
+        <v>96793</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13395,43 +13404,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ulva (Ulva), Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>620345</v>
+        <v>620352</v>
       </c>
       <c r="R103" t="n">
-        <v>6568134</v>
+        <v>6568133</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>01:01</t>
+          <t>00:55</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>01:01</t>
+          <t>00:55</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13503,6 +13503,384 @@
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>118123764</v>
+      </c>
+      <c r="B104" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ulva (Ulva), Srm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>620254</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6568245</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>118123718</v>
+      </c>
+      <c r="B105" t="n">
+        <v>57535</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ulva (Ulva), Srm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>620197</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6568097</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>118124029</v>
+      </c>
+      <c r="B106" t="n">
+        <v>96793</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ulva (Ulva), Srm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>620319</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6568185</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14014,6 +14014,268 @@
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>118842281</v>
+      </c>
+      <c r="B108" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Talludden (Talludden), Srm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>620006</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6568632</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>118842593</v>
+      </c>
+      <c r="B109" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Talludden (Talludden), Srm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>620031</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6568661</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14004,19 +14004,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Josefin Stagnell</t>
+          <t>Josefin Hagernäs</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Josefin Stagnell, Leif Persson</t>
+          <t>Josefin Hagernäs, Leif Persson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118842281</v>
+        <v>118842593</v>
       </c>
       <c r="B108" t="n">
         <v>97846</v>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -14070,10 +14070,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>620006</v>
+        <v>620031</v>
       </c>
       <c r="R108" t="n">
-        <v>6568632</v>
+        <v>6568661</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14147,7 +14147,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118842593</v>
+        <v>118842281</v>
       </c>
       <c r="B109" t="n">
         <v>97846</v>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>620031</v>
+        <v>620006</v>
       </c>
       <c r="R109" t="n">
-        <v>6568661</v>
+        <v>6568632</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14275,6 +14275,138 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>118893171</v>
+      </c>
+      <c r="B110" t="n">
+        <v>89906</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Ålpussen (Ålpussen), Srm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>619818</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6568478</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14016,7 +14016,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118842593</v>
+        <v>118842281</v>
       </c>
       <c r="B108" t="n">
         <v>97846</v>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -14070,10 +14070,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>620031</v>
+        <v>620006</v>
       </c>
       <c r="R108" t="n">
-        <v>6568661</v>
+        <v>6568632</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14147,7 +14147,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118842281</v>
+        <v>118842593</v>
       </c>
       <c r="B109" t="n">
         <v>97846</v>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>620006</v>
+        <v>620031</v>
       </c>
       <c r="R109" t="n">
-        <v>6568632</v>
+        <v>6568661</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14016,10 +14016,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118842281</v>
+        <v>118842593</v>
       </c>
       <c r="B108" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -14070,10 +14070,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>620006</v>
+        <v>620031</v>
       </c>
       <c r="R108" t="n">
-        <v>6568632</v>
+        <v>6568661</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14147,10 +14147,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118842593</v>
+        <v>118842281</v>
       </c>
       <c r="B109" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>620031</v>
+        <v>620006</v>
       </c>
       <c r="R109" t="n">
-        <v>6568661</v>
+        <v>6568632</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14281,7 +14281,7 @@
         <v>118893171</v>
       </c>
       <c r="B110" t="n">
-        <v>89906</v>
+        <v>89913</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14016,7 +14016,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118842593</v>
+        <v>118842281</v>
       </c>
       <c r="B108" t="n">
         <v>97853</v>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -14070,10 +14070,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>620031</v>
+        <v>620006</v>
       </c>
       <c r="R108" t="n">
-        <v>6568661</v>
+        <v>6568632</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14147,7 +14147,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118842281</v>
+        <v>118842593</v>
       </c>
       <c r="B109" t="n">
         <v>97853</v>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>620006</v>
+        <v>620031</v>
       </c>
       <c r="R109" t="n">
-        <v>6568632</v>
+        <v>6568661</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14621,6 +14621,258 @@
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>120403239</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91481</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>619770</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6568477</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>120402578</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91481</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>619755</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6568476</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14873,6 +14873,132 @@
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>120432064</v>
+      </c>
+      <c r="B115" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>619753</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6568538</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14623,7 +14623,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120403239</v>
+        <v>120402578</v>
       </c>
       <c r="B113" t="n">
         <v>91481</v>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -14672,10 +14672,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>619770</v>
+        <v>619755</v>
       </c>
       <c r="R113" t="n">
-        <v>6568477</v>
+        <v>6568476</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14707,7 +14707,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14749,7 +14749,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120402578</v>
+        <v>120403239</v>
       </c>
       <c r="B114" t="n">
         <v>91481</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -14798,10 +14798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>619755</v>
+        <v>619770</v>
       </c>
       <c r="R114" t="n">
-        <v>6568476</v>
+        <v>6568477</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14623,7 +14623,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120402578</v>
+        <v>120403239</v>
       </c>
       <c r="B113" t="n">
         <v>91481</v>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -14672,10 +14672,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>619755</v>
+        <v>619770</v>
       </c>
       <c r="R113" t="n">
-        <v>6568476</v>
+        <v>6568477</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14707,7 +14707,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14749,7 +14749,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120403239</v>
+        <v>120402578</v>
       </c>
       <c r="B114" t="n">
         <v>91481</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -14798,10 +14798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>619770</v>
+        <v>619755</v>
       </c>
       <c r="R114" t="n">
-        <v>6568477</v>
+        <v>6568476</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14999,6 +14999,439 @@
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120534504</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Strax O Skottvångsvägen: 350 m S Stora sjöstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>619794</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6568456</v>
+      </c>
+      <c r="S116" t="n">
+        <v>50</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Björn Carlsson, Lars-Olof Persson, Petter Kappel, Andreas Grabs</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120534423</v>
+      </c>
+      <c r="B117" t="n">
+        <v>86470</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Strax O Skottvångsvägen, 350 m S,Stora sjöstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>619671</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6568448</v>
+      </c>
+      <c r="S117" t="n">
+        <v>50</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Närmsta träd en tal, även granar i närheten</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Andreas Grabs, Petter Kappel, Lars-Olof Persson, Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120534709</v>
+      </c>
+      <c r="B118" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Strax O Skottvångsvägen: 350 m S Stora sjöstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>619794</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6568456</v>
+      </c>
+      <c r="S118" t="n">
+        <v>50</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Björn Carlsson, Andreas Grabs</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120538834</v>
+      </c>
+      <c r="B119" t="n">
+        <v>89256</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6268</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Rökmusseron</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Tricholoma fucatum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Strax O Skottvångsvägen: 350 m S Stora sjöstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>619794</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6568456</v>
+      </c>
+      <c r="S119" t="n">
+        <v>50</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Andreas Grabs, Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15222,10 +15222,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120534709</v>
+        <v>120538834</v>
       </c>
       <c r="B118" t="n">
-        <v>91879</v>
+        <v>89256</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15238,21 +15238,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5964</v>
+        <v>6268</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15321,17 +15321,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Björn Carlsson, Andreas Grabs</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Andreas Grabs, Björn Carlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120538834</v>
+        <v>120534709</v>
       </c>
       <c r="B119" t="n">
-        <v>89256</v>
+        <v>91879</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15344,21 +15344,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6268</v>
+        <v>5964</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Andreas Grabs, Björn Carlsson</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Björn Carlsson, Andreas Grabs</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15222,10 +15222,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120538834</v>
+        <v>120534709</v>
       </c>
       <c r="B118" t="n">
-        <v>89256</v>
+        <v>91879</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -15238,21 +15238,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6268</v>
+        <v>5964</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15321,17 +15321,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Andreas Grabs, Björn Carlsson</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Björn Carlsson, Andreas Grabs</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120534709</v>
+        <v>120538834</v>
       </c>
       <c r="B119" t="n">
-        <v>91879</v>
+        <v>89256</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -15344,21 +15344,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5964</v>
+        <v>6268</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Björn Carlsson, Andreas Grabs</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Katarina Hammarstedt, Lars-Olof Persson, Petter Kappel, Andreas Grabs, Björn Carlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15437,7 +15437,7 @@
         <v>121231416</v>
       </c>
       <c r="B120" t="n">
-        <v>4772</v>
+        <v>4775</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14520,7 +14520,7 @@
         <v>119395183</v>
       </c>
       <c r="B112" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14535,11 +14535,6 @@
       <c r="E112" t="n">
         <v>100138</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14520,7 +14520,7 @@
         <v>119395183</v>
       </c>
       <c r="B112" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -14534,6 +14534,11 @@
       </c>
       <c r="E112" t="n">
         <v>100138</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -14520,7 +14520,7 @@
         <v>119395183</v>
       </c>
       <c r="B112" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AY121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15574,6 +15574,137 @@
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>122923943</v>
+      </c>
+      <c r="B121" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Talludden, Talludden, Srm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>620021</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6568578</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Återfunnen. Ny lokal 20240417.</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15705,6 +15705,519 @@
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>123034100</v>
+      </c>
+      <c r="B122" t="n">
+        <v>83376</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>400 m N Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>620037</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6568373</v>
+      </c>
+      <c r="S122" t="n">
+        <v>100</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>123064028</v>
+      </c>
+      <c r="B123" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Ulva, Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>620190</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6568243</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123063997</v>
+      </c>
+      <c r="B124" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Ulva, Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>620240</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6568182</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123064071</v>
+      </c>
+      <c r="B125" t="n">
+        <v>91564</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Ulva, Ulva, Srm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>620206</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6568243</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,7 +15576,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122923943</v>
+        <v>123034100</v>
       </c>
       <c r="B121" t="n">
         <v>83376</v>
@@ -15611,27 +15611,25 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Talludden, Talludden, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620021</v>
+        <v>620037</v>
       </c>
       <c r="R121" t="n">
-        <v>6568578</v>
+        <v>6568373</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15655,27 +15653,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Återfunnen. Ny lokal 20240417.</t>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15684,33 +15672,29 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123034100</v>
+        <v>123064028</v>
       </c>
       <c r="B122" t="n">
-        <v>83376</v>
+        <v>98357</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15723,44 +15707,46 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620037</v>
+        <v>620190</v>
       </c>
       <c r="R122" t="n">
-        <v>6568373</v>
+        <v>6568243</v>
       </c>
       <c r="S122" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15787,14 +15773,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15803,29 +15794,33 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123064028</v>
+        <v>123063997</v>
       </c>
       <c r="B123" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15834,30 +15829,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -15871,10 +15866,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>620190</v>
+        <v>620240</v>
       </c>
       <c r="R123" t="n">
-        <v>6568243</v>
+        <v>6568182</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15906,7 +15901,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15916,7 +15911,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15948,10 +15943,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123063997</v>
+        <v>123064071</v>
       </c>
       <c r="B124" t="n">
-        <v>105463</v>
+        <v>91564</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15964,31 +15959,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -15997,10 +15992,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620240</v>
+        <v>620206</v>
       </c>
       <c r="R124" t="n">
-        <v>6568182</v>
+        <v>6568243</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16032,7 +16027,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16042,7 +16037,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16057,6 +16052,26 @@
       <c r="AH124" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -16074,10 +16089,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123064071</v>
+        <v>122923943</v>
       </c>
       <c r="B125" t="n">
-        <v>91564</v>
+        <v>83376</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -16086,30 +16101,30 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -16117,16 +16132,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>Talludden, Talludden, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>620206</v>
+        <v>620021</v>
       </c>
       <c r="R125" t="n">
-        <v>6568243</v>
+        <v>6568578</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16153,22 +16170,27 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Återfunnen. Ny lokal 20240417.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16177,32 +16199,13 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,10 +15576,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123034100</v>
+        <v>123063997</v>
       </c>
       <c r="B121" t="n">
-        <v>83376</v>
+        <v>105471</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15588,48 +15588,50 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620037</v>
+        <v>620240</v>
       </c>
       <c r="R121" t="n">
-        <v>6568373</v>
+        <v>6568182</v>
       </c>
       <c r="S121" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15656,14 +15658,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15672,29 +15679,33 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123064028</v>
+        <v>123064071</v>
       </c>
       <c r="B122" t="n">
-        <v>98357</v>
+        <v>91572</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15703,35 +15714,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -15740,7 +15751,7 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620190</v>
+        <v>620206</v>
       </c>
       <c r="R122" t="n">
         <v>6568243</v>
@@ -15775,7 +15786,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15785,7 +15796,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15800,6 +15811,26 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15817,10 +15848,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123063997</v>
+        <v>123034100</v>
       </c>
       <c r="B123" t="n">
-        <v>105463</v>
+        <v>83376</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15829,50 +15860,48 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>620240</v>
+        <v>620037</v>
       </c>
       <c r="R123" t="n">
-        <v>6568182</v>
+        <v>6568373</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15899,19 +15928,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15920,33 +15944,29 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123064071</v>
+        <v>123064028</v>
       </c>
       <c r="B124" t="n">
-        <v>91564</v>
+        <v>98365</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15955,35 +15975,35 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -15992,7 +16012,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620206</v>
+        <v>620190</v>
       </c>
       <c r="R124" t="n">
         <v>6568243</v>
@@ -16027,7 +16047,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16037,7 +16057,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16052,26 +16072,6 @@
       <c r="AH124" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,10 +15576,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123063997</v>
+        <v>123034100</v>
       </c>
       <c r="B121" t="n">
-        <v>105471</v>
+        <v>83376</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15588,50 +15588,48 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620240</v>
+        <v>620037</v>
       </c>
       <c r="R121" t="n">
-        <v>6568182</v>
+        <v>6568373</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15658,19 +15656,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15679,33 +15672,29 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123064071</v>
+        <v>123063997</v>
       </c>
       <c r="B122" t="n">
-        <v>91572</v>
+        <v>105471</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15718,31 +15707,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -15751,10 +15740,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620206</v>
+        <v>620240</v>
       </c>
       <c r="R122" t="n">
-        <v>6568243</v>
+        <v>6568182</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15786,7 +15775,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15796,7 +15785,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15811,26 +15800,6 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15848,10 +15817,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123034100</v>
+        <v>123064028</v>
       </c>
       <c r="B123" t="n">
-        <v>83376</v>
+        <v>98365</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15864,44 +15833,46 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>620037</v>
+        <v>620190</v>
       </c>
       <c r="R123" t="n">
-        <v>6568373</v>
+        <v>6568243</v>
       </c>
       <c r="S123" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15928,14 +15899,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15944,29 +15920,33 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123064028</v>
+        <v>123064071</v>
       </c>
       <c r="B124" t="n">
-        <v>98365</v>
+        <v>91572</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15975,35 +15955,35 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -16012,7 +15992,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620190</v>
+        <v>620206</v>
       </c>
       <c r="R124" t="n">
         <v>6568243</v>
@@ -16047,7 +16027,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -16057,7 +16037,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16072,6 +16052,26 @@
       <c r="AH124" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,10 +15576,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123034100</v>
+        <v>123063997</v>
       </c>
       <c r="B121" t="n">
-        <v>83376</v>
+        <v>105471</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15588,48 +15588,50 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620037</v>
+        <v>620240</v>
       </c>
       <c r="R121" t="n">
-        <v>6568373</v>
+        <v>6568182</v>
       </c>
       <c r="S121" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15656,14 +15658,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15672,29 +15679,33 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123063997</v>
+        <v>123034100</v>
       </c>
       <c r="B122" t="n">
-        <v>105471</v>
+        <v>83376</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15703,50 +15714,48 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620240</v>
+        <v>620037</v>
       </c>
       <c r="R122" t="n">
-        <v>6568182</v>
+        <v>6568373</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15773,19 +15782,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15794,23 +15798,19 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15702,10 +15702,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123034100</v>
+        <v>123064071</v>
       </c>
       <c r="B122" t="n">
-        <v>83376</v>
+        <v>91572</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15714,48 +15714,50 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1445</v>
+        <v>1339</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620037</v>
+        <v>620206</v>
       </c>
       <c r="R122" t="n">
-        <v>6568373</v>
+        <v>6568243</v>
       </c>
       <c r="S122" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15782,14 +15784,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15798,19 +15805,43 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -15943,10 +15974,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123064071</v>
+        <v>123034100</v>
       </c>
       <c r="B124" t="n">
-        <v>91572</v>
+        <v>83376</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15955,50 +15986,48 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620206</v>
+        <v>620037</v>
       </c>
       <c r="R124" t="n">
-        <v>6568243</v>
+        <v>6568373</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -16025,19 +16054,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>15:48</t>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16046,43 +16070,19 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15579,7 +15579,7 @@
         <v>123063997</v>
       </c>
       <c r="B121" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15702,10 +15702,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123064071</v>
+        <v>123064028</v>
       </c>
       <c r="B122" t="n">
-        <v>91572</v>
+        <v>98368</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15714,35 +15714,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -15751,7 +15751,7 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620206</v>
+        <v>620190</v>
       </c>
       <c r="R122" t="n">
         <v>6568243</v>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15811,26 +15811,6 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15848,10 +15828,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123064028</v>
+        <v>123064071</v>
       </c>
       <c r="B123" t="n">
-        <v>98365</v>
+        <v>91575</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15860,35 +15840,35 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -15897,7 +15877,7 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>620190</v>
+        <v>620206</v>
       </c>
       <c r="R123" t="n">
         <v>6568243</v>
@@ -15932,7 +15912,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15942,7 +15922,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15957,6 +15937,26 @@
       <c r="AH123" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15977,7 +15977,7 @@
         <v>123034100</v>
       </c>
       <c r="B124" t="n">
-        <v>83376</v>
+        <v>83379</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>122923943</v>
       </c>
       <c r="B125" t="n">
-        <v>83376</v>
+        <v>83379</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,10 +15576,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123063997</v>
+        <v>123034100</v>
       </c>
       <c r="B121" t="n">
-        <v>105474</v>
+        <v>83381</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15588,50 +15588,48 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620240</v>
+        <v>620037</v>
       </c>
       <c r="R121" t="n">
-        <v>6568182</v>
+        <v>6568373</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15658,19 +15656,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15679,33 +15672,29 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123064028</v>
+        <v>123064071</v>
       </c>
       <c r="B122" t="n">
-        <v>98368</v>
+        <v>91577</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15714,35 +15703,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -15751,7 +15740,7 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620190</v>
+        <v>620206</v>
       </c>
       <c r="R122" t="n">
         <v>6568243</v>
@@ -15786,7 +15775,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15796,7 +15785,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15811,6 +15800,26 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -15828,10 +15837,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123064071</v>
+        <v>123064028</v>
       </c>
       <c r="B123" t="n">
-        <v>91575</v>
+        <v>98370</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15840,35 +15849,35 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -15877,7 +15886,7 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>620206</v>
+        <v>620190</v>
       </c>
       <c r="R123" t="n">
         <v>6568243</v>
@@ -15912,7 +15921,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15922,7 +15931,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15937,26 +15946,6 @@
       <c r="AH123" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15974,10 +15963,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123034100</v>
+        <v>123063997</v>
       </c>
       <c r="B124" t="n">
-        <v>83379</v>
+        <v>105476</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15986,48 +15975,50 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620037</v>
+        <v>620240</v>
       </c>
       <c r="R124" t="n">
-        <v>6568373</v>
+        <v>6568182</v>
       </c>
       <c r="S124" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -16054,14 +16045,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16070,19 +16066,23 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
         <v>122923943</v>
       </c>
       <c r="B125" t="n">
-        <v>83379</v>
+        <v>83381</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,10 +15576,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123034100</v>
+        <v>123063997</v>
       </c>
       <c r="B121" t="n">
-        <v>83381</v>
+        <v>105482</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15588,48 +15588,50 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620037</v>
+        <v>620240</v>
       </c>
       <c r="R121" t="n">
-        <v>6568373</v>
+        <v>6568182</v>
       </c>
       <c r="S121" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15656,14 +15658,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15672,19 +15679,23 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -15694,7 +15705,7 @@
         <v>123064071</v>
       </c>
       <c r="B122" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15840,7 +15851,7 @@
         <v>123064028</v>
       </c>
       <c r="B123" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15963,10 +15974,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123063997</v>
+        <v>123034100</v>
       </c>
       <c r="B124" t="n">
-        <v>105476</v>
+        <v>83383</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15975,50 +15986,48 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620240</v>
+        <v>620037</v>
       </c>
       <c r="R124" t="n">
-        <v>6568182</v>
+        <v>6568373</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -16045,19 +16054,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16066,23 +16070,19 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
         <v>122923943</v>
       </c>
       <c r="B125" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,10 +15576,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123063997</v>
+        <v>123064071</v>
       </c>
       <c r="B121" t="n">
-        <v>105482</v>
+        <v>91586</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15592,31 +15592,31 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620240</v>
+        <v>620206</v>
       </c>
       <c r="R121" t="n">
-        <v>6568182</v>
+        <v>6568243</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15685,6 +15685,26 @@
       <c r="AH121" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15702,10 +15722,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123064071</v>
+        <v>123034100</v>
       </c>
       <c r="B122" t="n">
-        <v>91583</v>
+        <v>83386</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15714,50 +15734,48 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620206</v>
+        <v>620037</v>
       </c>
       <c r="R122" t="n">
-        <v>6568243</v>
+        <v>6568373</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15784,19 +15802,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>15:48</t>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15805,43 +15818,19 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -15851,7 +15840,7 @@
         <v>123064028</v>
       </c>
       <c r="B123" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15974,10 +15963,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123034100</v>
+        <v>123063997</v>
       </c>
       <c r="B124" t="n">
-        <v>83383</v>
+        <v>105485</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15986,48 +15975,50 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620037</v>
+        <v>620240</v>
       </c>
       <c r="R124" t="n">
-        <v>6568373</v>
+        <v>6568182</v>
       </c>
       <c r="S124" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -16054,14 +16045,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16070,19 +16066,23 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
         <v>122923943</v>
       </c>
       <c r="B125" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,10 +15576,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123064071</v>
+        <v>123064028</v>
       </c>
       <c r="B121" t="n">
-        <v>91586</v>
+        <v>98396</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15588,35 +15588,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -15625,7 +15625,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620206</v>
+        <v>620190</v>
       </c>
       <c r="R121" t="n">
         <v>6568243</v>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15685,26 +15685,6 @@
       <c r="AH121" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -15722,10 +15702,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123034100</v>
+        <v>123063997</v>
       </c>
       <c r="B122" t="n">
-        <v>83386</v>
+        <v>105502</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15734,48 +15714,50 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1445</v>
+        <v>221144</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620037</v>
+        <v>620240</v>
       </c>
       <c r="R122" t="n">
-        <v>6568373</v>
+        <v>6568182</v>
       </c>
       <c r="S122" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15802,14 +15784,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15818,29 +15805,33 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123063997</v>
+        <v>123064071</v>
       </c>
       <c r="B123" t="n">
-        <v>105485</v>
+        <v>91603</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15853,31 +15844,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -15886,10 +15877,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>620240</v>
+        <v>620206</v>
       </c>
       <c r="R123" t="n">
-        <v>6568182</v>
+        <v>6568243</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15921,7 +15912,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15931,7 +15922,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15946,6 +15937,26 @@
       <c r="AH123" t="inlineStr">
         <is>
           <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -15963,10 +15974,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123064028</v>
+        <v>123034100</v>
       </c>
       <c r="B124" t="n">
-        <v>98379</v>
+        <v>83395</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15979,46 +15990,44 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>1445</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620190</v>
+        <v>620037</v>
       </c>
       <c r="R124" t="n">
-        <v>6568243</v>
+        <v>6568373</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -16045,19 +16054,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>15:52</t>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16066,23 +16070,19 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
         <v>122923943</v>
       </c>
       <c r="B125" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -15576,10 +15576,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123064028</v>
+        <v>123063997</v>
       </c>
       <c r="B121" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15588,30 +15588,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>620190</v>
+        <v>620240</v>
       </c>
       <c r="R121" t="n">
-        <v>6568243</v>
+        <v>6568182</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15702,10 +15702,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123063997</v>
+        <v>123034100</v>
       </c>
       <c r="B122" t="n">
-        <v>105502</v>
+        <v>83400</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15714,50 +15714,48 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221144</v>
+        <v>1445</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ulva, Ulva, Srm</t>
+          <t>400 m N Ulva, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>620240</v>
+        <v>620037</v>
       </c>
       <c r="R122" t="n">
-        <v>6568182</v>
+        <v>6568373</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15784,19 +15782,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15805,23 +15798,19 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -15831,7 +15820,7 @@
         <v>123064071</v>
       </c>
       <c r="B123" t="n">
-        <v>91603</v>
+        <v>91608</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15974,10 +15963,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123034100</v>
+        <v>123064028</v>
       </c>
       <c r="B124" t="n">
-        <v>83395</v>
+        <v>98502</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15990,44 +15979,46 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>400 m N Ulva, Srm</t>
+          <t>Ulva, Ulva, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>620037</v>
+        <v>620190</v>
       </c>
       <c r="R124" t="n">
-        <v>6568373</v>
+        <v>6568243</v>
       </c>
       <c r="S124" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -16054,14 +16045,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Återfynd Exkursion med Strängnäs svampklubb</t>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16070,19 +16066,23 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lars Ekqvist</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lars Ekqvist, Birgitta Arwidsson, Wijdan Cederlid, Björn Carlsson, Lars-Olof Persson</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
         <v>122923943</v>
       </c>
       <c r="B125" t="n">
-        <v>83395</v>
+        <v>83400</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 11562-2024 artfynd.xlsx
+++ b/artfynd/A 11562-2024 artfynd.xlsx
@@ -16092,7 +16092,7 @@
         <v>122923943</v>
       </c>
       <c r="B125" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
